--- a/Lab work/Lab7_Kuntal Das.xlsx
+++ b/Lab work/Lab7_Kuntal Das.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anudip Foundation\Lab work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69A02D6-DC82-4116-A0B5-433891141310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C4961-40DD-4790-AD46-288ED41860D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B5B8E237-C597-4DE4-B164-68D53E1E8D6A}"/>
   </bookViews>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -212,16 +212,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{1FB35606-1480-4D1B-8558-E519BB4EF6DC}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -697,20 +699,20 @@
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
@@ -900,17 +902,17 @@
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
     <row r="17" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G17" s="2" t="s">
@@ -925,7 +927,7 @@
       <c r="J17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G18" s="3">
@@ -1057,16 +1059,16 @@
       <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
